--- a/02_加值成品/九上/九上6-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上6-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上6-1 地球內部與板塊　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三上學期 九上6-1 地球內部與板塊　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>地球內部由外而內分？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>地殼地函地核</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>地震火山</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>不同</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>板塊</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>三層</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>地球最外層是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>地殼地函地核</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>地核</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>板塊</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>地殼</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>最薄</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>地球最深處是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>地震與火山</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>地殼</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>地核</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>少</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>中心</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>地表由多個什麼組成？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>少</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>板塊</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>不同</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>地核</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>拼合</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>板塊會不會移動？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>很緩慢</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>地殼</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>會緩慢移動</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>板塊交界</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>移動</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>板塊交界處常有？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>地震與火山</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>不同</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>地殼</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>很緩慢</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>活躍</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>臺灣位於什麼位置？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>板塊交界</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>地殼地函地核</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>地殼</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>位板塊交界</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>活躍帶</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>地殼與地核哪個厚？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>板塊</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>地核</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>位板塊交界</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>不同</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>較深</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>地球最外層的固體是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>位板塊交界</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>板塊</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>地核</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>地殼</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>最薄</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>板塊之間相互擠壓處常發生？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>地核</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>地震火山</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>地殼地函地核</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>軟流圈</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>交界</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上6-1 地球內部與板塊　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三上學期 九上6-1 地球內部與板塊　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>板塊漂浮在什麼之上？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>軟流圈</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>很緩慢</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>較少</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>板塊交界</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>可流動</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>為何臺灣多地震？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>位板塊交界</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>地震與火山</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>地核</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>地殼</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>活躍</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>地函位於哪兩層之間？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>板塊互相擠壓摩擦釋放能量</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>板塊擠壓抬升形成山脈</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>地球內部熱對流</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>地殼與地核之間</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>中間</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>板塊移動速度如何？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>較少</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>板塊交界</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>很緩慢</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>地殼</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>漸進</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>火山常出現在哪裡？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>不同</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>板塊交界</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>地核</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>少</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>活躍帶</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>地質活動活躍處多在？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>地震火山</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>板塊交界</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>地核</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>軟流圈</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>邊界</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>地球內部各層性質？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>不同</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>地殼</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>軟流圈</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>地殼地函地核</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>分層</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>板塊交界遠離處地震？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>會緩慢移動</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>地殼地函地核</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>地核</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>較少</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>穩定</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>臺灣多地震是因為位於？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>板塊交界</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>很緩慢</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>少</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>地震與火山</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>活躍帶</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>地球內部三層由外而內為？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>地殼地函地核</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>板塊</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>地震火山</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>地核</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>分層</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上6-1 地球內部與板塊　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三上學期 九上6-1 地球內部與板塊　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何板塊交界地震火山頻繁？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>板塊擠壓抬升形成山脈</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>不同層密度性質使波速改變</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>地球內部熱對流</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>板塊互相擠壓摩擦釋放能量</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>應力</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>用地球分層說明地震波傳播差異？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>不同層密度性質使波速改變</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>歐亞與菲律賓海板塊交界多地震</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>地殼與地核之間</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>板塊擠壓抬升形成山脈</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>波</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>臺灣位處哪些板塊交界影響地質？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>板塊擠壓抬升形成山脈</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>地殼與地核之間</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>板塊互相擠壓摩擦釋放能量</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>歐亞與菲律賓海板塊交界多地震</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>位置</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>板塊移動如何造就高山？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>板塊互相擠壓摩擦釋放能量</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>地球內部熱對流</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>歐亞與菲律賓海板塊交界多地震</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>板塊擠壓抬升形成山脈</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>造山</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>為何地殼薄卻是人類活動所在？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>板塊互相擠壓摩擦釋放能量</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>地殼與地核之間</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>歐亞與菲律賓海板塊交界多地震</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>地殼是最外固體層</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>分布</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>板塊會移動的能量來源大致為？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>歐亞與菲律賓海板塊交界多地震</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>移高中,國中認識現象為主</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>地殼是最外固體層</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>地球內部熱對流</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>動力</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>地質活躍帶與板塊分布關係？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>歐亞與菲律賓海板塊交界多地震</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>地殼與地核之間</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>活躍帶多沿板塊交界分布</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>不同層密度性質使波速改變</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>關聯</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>為何課綱移除板塊學說細節？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>移高中,國中認識現象為主</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>不同層密度性質使波速改變</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>板塊擠壓抬升形成山脈</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>地殼是最外固體層</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>課綱</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>遠離板塊交界的地區地震較？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>少</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>位板塊交界</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>地震與火山</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>板塊</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>穩定</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>板塊緩慢移動的動力大致來自？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>地球內部熱對流</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>活躍帶多沿板塊交界分布</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>不同層密度性質使波速改變</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>地殼與地核之間</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>動力</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九上/九上6-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上6-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>三層</t>
+          <t>三層：從外面往裡面數,地球內部依序分成地殼、地函、地核三層</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>最薄</t>
+          <t>最薄：地殼是包在地球最外面的一層,也是三層中最薄的一層</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>中心</t>
+          <t>中心：地核位於地球最中心的位置,是離地表最深的地方</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>拼合</t>
+          <t>拼合：地球表面像拼圖一樣,由好幾塊大大小小的板塊拼合而成</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>移動</t>
+          <t>移動：板塊並不是固定不動的,它們會以非常緩慢的速度持續移動</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>活躍</t>
+          <t>活躍：板塊互相擠壓碰撞的交界處,地質活動特別活躍,常常發生地震和火山噴發</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>活躍帶</t>
+          <t>活躍帶：臺灣剛好位在板塊互相碰撞的交界地帶,所以地質活動比較頻繁</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>較深</t>
+          <t>較深：地核佔的範圍比地殼大很多,厚度也遠比薄薄的地殼要厚</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>最薄</t>
+          <t>最薄：地殼是地球構造中最外層、也是相對最薄的一層固體岩石</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>交界</t>
+          <t>交界：板塊邊界因為板塊相互擠壓、張裂或錯動,容易累積能量並釋放,因此常伴隨地震和火山活動</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>可流動</t>
+          <t>可流動：板塊是浮在地函裡一層比較黏稠、能緩慢流動的軟流圈上面</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>活躍</t>
+          <t>活躍：臺灣正好處在板塊碰撞擠壓的交界處,累積的能量釋放就形成地震</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>中間</t>
+          <t>中間：地函是夾在最外層地殼和最中心地核之間的一大層</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>漸進</t>
+          <t>漸進：板塊每年大約只移動幾公分,速度非常緩慢,要經過很久才能看出明顯改變</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>活躍帶</t>
+          <t>活躍帶：板塊交界處地底岩漿容易衝出地表,所以火山常常出現在這些地帶</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>邊界</t>
+          <t>邊界：板塊互相碰撞或分離的邊界地帶,地質活動特別頻繁活躍</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>分層</t>
+          <t>分層：地殼地函地核的溫度、壓力、物質狀態都不一樣,所以才會分成不同層次</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>穩定</t>
+          <t>穩定：距離板塊交界越遠的地方,受到的擠壓碰撞越少,地質也相對比較穩定</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>活躍帶</t>
+          <t>活躍帶：臺灣剛好位於歐亞板塊與菲律賓海板塊的交界處,板塊擠壓活動頻繁,所以地震特別多</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>分層</t>
+          <t>分層：地球內部由外往內大致分成地殼、地函、地核三層,各層的物質狀態和溫度都不同</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>應力</t>
+          <t>應力：板塊在交界處互相擠壓摩擦,累積的巨大能量會突然釋放出來,造成地震和火山活動</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>波</t>
+          <t>波：地殼地函地核的密度和物質狀態不同,地震波經過不同層時速度和方向會跟著改變</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>位置</t>
+          <t>位置：臺灣正好位在歐亞板塊和菲律賓海板塊互相碰撞的交界,所以地震特別多</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>造山</t>
+          <t>造山：兩個板塊互相擠壓時,地層被推擠隆起抬升,長期累積就形成高聳的山脈</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>分布</t>
+          <t>分布：地殼雖然是三層中最薄的,但它是最外面能站立居住的固體層,人類自然生活在地殼上</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>動力</t>
+          <t>動力：地球內部溫度很高,熱量產生對流循環,這股力量推動著板塊緩慢移動</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>關聯</t>
+          <t>關聯：把世界上容易發生地震火山的地帶畫出來,會發現它們大多沿著板塊交界線分布</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>課綱</t>
+          <t>課綱：詳細的板塊構造學說內容比較複雜,課程安排把它留到高中,國中先認識基本現象就好</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>穩定</t>
+          <t>穩定：板塊交界處是能量容易累積釋放的地方,離交界越遠的區域地殼相對穩定,地震通常較少</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>動力</t>
+          <t>動力：地球內部地函物質受熱產生緩慢的對流運動,這股力量帶動上方的板塊緩慢移動</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九上/九上6-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上6-1_三種難度測驗卷.xlsx
@@ -568,17 +568,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>板塊</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>會緩慢移動</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
           <t>地震火山</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>不同</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>板塊</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -603,17 +603,17 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>地殼地函地核</t>
+          <t>位板塊交界</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>地核</t>
+          <t>地震火山</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>板塊</t>
+          <t>地震與火山</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>地殼</t>
+          <t>板塊交界</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>少</t>
+          <t>會緩慢移動</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>少</t>
+          <t>地殼地函地核</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>不同</t>
+          <t>地核</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>地核</t>
+          <t>軟流圈</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>地殼地函地核</t>
+          <t>地核</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>位板塊交界</t>
+          <t>會緩慢移動</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>位板塊交界</t>
+          <t>軟流圈</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>不同</t>
+          <t>地震與火山</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -883,17 +883,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>位板塊交界</t>
+          <t>板塊</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>板塊</t>
+          <t>不同</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>地核</t>
+          <t>很緩慢</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>地震與火山</t>
+          <t>地震火山</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>地核</t>
+          <t>較少</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>地殼</t>
+          <t>不同</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>不同</t>
+          <t>地殼</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>地核</t>
+          <t>地殼地函地核</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>少</t>
+          <t>地震與火山</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>地震火山</t>
+          <t>地殼</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -1249,12 +1249,12 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>地核</t>
+          <t>軟流圈</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>軟流圈</t>
+          <t>地震與火山</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1319,17 +1319,17 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>會緩慢移動</t>
+          <t>地震與火山</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>地殼地函地核</t>
+          <t>地殼</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>地核</t>
+          <t>板塊</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>很緩慢</t>
+          <t>地殼</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>少</t>
+          <t>地震火山</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>地震與火山</t>
+          <t>會緩慢移動</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1404,17 +1404,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
+          <t>會緩慢移動</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
           <t>板塊</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>地震火山</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>地核</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>位板塊交界</t>
+          <t>會緩慢移動</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>地震與火山</t>
+          <t>板塊交界</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>板塊</t>
+          <t>地震火山</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
